--- a/results/Int All Data 0.5/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.5/Linea_fi_all.xlsx
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0008857395925597866 +/- 0.0001980573939326625</t>
+          <t>0.0008414526129317923 +/- 0.00013286093888394967</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.027887712839392554 +/- 0.0028753795401404983</t>
+          <t>0.027795674183156927 +/- 0.002911972760157645</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -3011,74 +3011,74 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
+          <t>0.005107778819119013 +/- 0.002695590818794669</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-0.0022492970946579537 +/- 0.001084895679736685</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.0012652296157450783 +/- 0.0010899440815007465</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>4.686035613868933e-05 +/- 0.0004892364812047949</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>-0.00829428303655112 +/- 0.0013589503280225035</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.008575445173383277 +/- 0.0009383779003983489</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.028303655107778804 +/- 0.001639442894520689</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.07567947516401122 +/- 0.004341859188340603</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.33013120899718834 +/- 0.004973603762960413</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>-0.0003280224929709585 +/- 0.0006304416142021284</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.2611527647610121 +/- 0.00639107231014334</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.001452671040299902 +/- 0.0007091258645933285</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-9.372071227742307e-05 +/- 0.00018744142455484614</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>0.005154639175257725 +/- 0.0027162843010664203</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-0.0022492970946579537 +/- 0.001084895679736685</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0.0012652296157450783 +/- 0.0010899440815007465</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>4.686035613868933e-05 +/- 0.0004892364812047949</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>-0.00829428303655112 +/- 0.0013589503280225035</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>0.008575445173383277 +/- 0.0009383779003983489</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0.028303655107778804 +/- 0.001639442894520689</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.07567947516401122 +/- 0.004341859188340603</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>0.33013120899718834 +/- 0.004973603762960413</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>-0.0003280224929709585 +/- 0.0006304416142021284</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>0.2611527647610121 +/- 0.00639107231014334</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.001452671040299902 +/- 0.0007091258645933285</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-9.372071227742307e-05 +/- 0.00018744142455484614</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.005107778819119013 +/- 0.002695590818794669</t>
-        </is>
-      </c>
       <c r="BO4" t="inlineStr">
         <is>
           <t>0.06429240862230548 +/- 0.0028642374489102366</t>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>0.2298500468603561 +/- 0.006142997706121743</t>
+          <t>0.22989690721649483 +/- 0.00605279096249955</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.04587682672233817 +/- 0.00327148934117217</t>
+          <t>0.04598121085594986 +/- 0.003296374253577871</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.005062630480166974 +/- 0.0014397822780932788</t>
+          <t>0.005114822546972819 +/- 0.0013965645261231258</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.001934874941009934 +/- 0.0009065300949645485</t>
+          <t>0.0018876828692779846 +/- 0.0009671496711618428</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -4891,74 +4891,74 @@
       </c>
       <c r="DO6" t="inlineStr">
         <is>
+          <t>0.017791411042944794 +/- 0.0037341425686075124</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>-0.0017461066540821134 +/- 0.002152806933073529</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>0.00018876828692779846 +/- 0.0004812665892961631</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>0.00018876828692779846 +/- 0.0004812665892961631</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>-9.438414346389923e-05 +/- 0.0004623859825923942</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>0.0806512505899009 +/- 0.005218726242725129</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>0.1084473808400189 +/- 0.005755885262289502</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>-0.0005191127890514458 +/- 0.0011835711377050123</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>0.0007078810759792442 +/- 0.0019486383031677992</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>0.15172251061821615 +/- 0.0066245634312711126</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>0.002737140160453078 +/- 0.0006935789738885913</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
           <t>0.017744218971212845 +/- 0.003705103619894378</t>
         </is>
       </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>-0.0017461066540821134 +/- 0.002152806933073529</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0.00018876828692779846 +/- 0.0004812665892961631</t>
-        </is>
-      </c>
-      <c r="DR6" t="inlineStr">
-        <is>
-          <t>0.00018876828692779846 +/- 0.0004812665892961631</t>
-        </is>
-      </c>
-      <c r="DS6" t="inlineStr">
-        <is>
-          <t>-9.438414346389923e-05 +/- 0.0004623859825923942</t>
-        </is>
-      </c>
-      <c r="DT6" t="inlineStr">
-        <is>
-          <t>0.0806512505899009 +/- 0.005218726242725129</t>
-        </is>
-      </c>
-      <c r="DU6" t="inlineStr">
-        <is>
-          <t>0.1084473808400189 +/- 0.005755885262289502</t>
-        </is>
-      </c>
-      <c r="DV6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DW6" t="inlineStr">
-        <is>
-          <t>-0.0005191127890514458 +/- 0.0011835711377050123</t>
-        </is>
-      </c>
-      <c r="DX6" t="inlineStr">
-        <is>
-          <t>0.0007078810759792442 +/- 0.0019486383031677992</t>
-        </is>
-      </c>
-      <c r="DY6" t="inlineStr">
-        <is>
-          <t>0.15172251061821615 +/- 0.0066245634312711126</t>
-        </is>
-      </c>
-      <c r="DZ6" t="inlineStr">
-        <is>
-          <t>0.002737140160453078 +/- 0.0006935789738885913</t>
-        </is>
-      </c>
-      <c r="EA6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="EB6" t="inlineStr">
-        <is>
-          <t>0.017744218971212845 +/- 0.003705103619894378</t>
-        </is>
-      </c>
       <c r="EC6" t="inlineStr">
         <is>
           <t>0.006842850401132606 +/- 0.0032983848522900394</t>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>0.008966493629070326 +/- 0.0019910356875629067</t>
+          <t>0.009013685700802276 +/- 0.002051091440500307</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.010278170674210241 +/- 0.0032651182825423654</t>
+          <t>0.010136727958510094 +/- 0.003185515498653276</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>-0.00542197076850548 +/- 0.0011006711485081195</t>
+          <t>-0.005327675624705386 +/- 0.0009900990099009788</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0072046109510086834 +/- 0.0010952693804987044</t>
+          <t>0.0071565802113352835 +/- 0.0010621202875838683</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.0008037079985918099</t>
+          <t>4.803073967343252e-05 +/- 0.0007877627025387454</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>0.05427473583093184 +/- 0.004402090004760645</t>
+          <t>0.05422670509125845 +/- 0.004388706171570541</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0015223097112860185 +/- 0.0004360432473972858</t>
+          <t>-0.0014698162729658182 +/- 0.0005143285549150962</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.00036745406824146843 +/- 0.0003361220072143091</t>
+          <t>-0.00031496062992125706 +/- 0.0003482020777275868</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.006096408317580304 +/- 0.0023482529770897562</t>
+          <t>0.006143667296786348 +/- 0.002246666223819422</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.008648393194707027 +/- 0.001480194684628128</t>
+          <t>-0.008695652173913082 +/- 0.0014673132983232303</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
